--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486755_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486755_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.7487</v>
+        <v>6.914</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4053</v>
+        <v>8.446400000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6566</v>
+        <v>-1.5324</v>
       </c>
       <c r="G2" t="n">
         <v>3.5076</v>
@@ -610,13 +610,13 @@
         <v>2.7031</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1104</v>
+        <v>1.0549</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6071</v>
+        <v>0.434</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4967</v>
+        <v>0.6209</v>
       </c>
       <c r="V2" t="n">
         <v>0.6138</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5795</v>
+        <v>5.49</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9535</v>
+        <v>6.4915</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.374</v>
+        <v>-1.0015</v>
       </c>
       <c r="G3" t="n">
         <v>3.198</v>
@@ -688,13 +688,13 @@
         <v>1.9308</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1305</v>
+        <v>1.0411</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2406</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1101</v>
+        <v>0.2624</v>
       </c>
       <c r="V3" t="n">
         <v>0.2856</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8367</v>
+        <v>3.7195</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3828</v>
+        <v>1.3897</v>
       </c>
       <c r="F4" t="n">
-        <v>2.454</v>
+        <v>2.3298</v>
       </c>
       <c r="G4" t="n">
         <v>0.9265</v>
@@ -766,13 +766,13 @@
         <v>2.1239</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5241</v>
+        <v>0.4069</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1384</v>
+        <v>-0.1314</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6625</v>
+        <v>0.5383</v>
       </c>
       <c r="V4" t="n">
         <v>1.2277</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. HERRERO ALONSO</t>
+          <t>J. SECO YANES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3255</v>
+        <v>1.4279</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5366</v>
+        <v>1.1166</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8621</v>
+        <v>0.3113</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.421</v>
+        <v>0.668</v>
       </c>
       <c r="H5" t="n">
-        <v>3.2833</v>
+        <v>-0.0554</v>
       </c>
       <c r="I5" t="n">
-        <v>-4.7043</v>
+        <v>0.7234</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0979</v>
+        <v>1.3442</v>
       </c>
       <c r="K5" t="n">
-        <v>5.1465</v>
+        <v>0.0828</v>
       </c>
       <c r="L5" t="n">
-        <v>-4.0486</v>
+        <v>1.2615</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.5189</v>
+        <v>-0.6763</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.8632</v>
+        <v>-0.1382</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.5381</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3515</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.2565</v>
+        <v>0.1034</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3856</v>
+        <v>-0.2277</v>
       </c>
       <c r="U5" t="n">
-        <v>1.871</v>
+        <v>0.3311</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8415</v>
+        <v>0.6565</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8415</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SECO YANES</t>
+          <t>J. DEL CASTILLO LEON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1258</v>
+        <v>0.9517</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0131</v>
+        <v>0.7528</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1126</v>
+        <v>0.1989</v>
       </c>
       <c r="G6" t="n">
-        <v>0.668</v>
+        <v>1.7834</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0554</v>
+        <v>0.6554</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7234</v>
+        <v>1.128</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3442</v>
+        <v>2.7293</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0828</v>
+        <v>1.3458</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2615</v>
+        <v>1.3835</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6763</v>
+        <v>-0.9459</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1382</v>
+        <v>-0.6904</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5381</v>
+        <v>-0.2555</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.9308</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1987</v>
+        <v>0.1104</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3311</v>
+        <v>-0.3313</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1324</v>
+        <v>0.4417</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6565</v>
+        <v>-0.9421</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6565</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.635</v>
+        <v>0.8378</v>
       </c>
       <c r="E7" t="n">
-        <v>0.503</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.132</v>
+        <v>0.2313</v>
       </c>
       <c r="G7" t="n">
         <v>-1.5939</v>
@@ -1000,13 +1000,13 @@
         <v>0.9654</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2924</v>
+        <v>-0.0897</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2207</v>
+        <v>-0.1173</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0717</v>
+        <v>0.0277</v>
       </c>
       <c r="V7" t="n">
         <v>1.5559</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. DEL CASTILLO LEON</t>
+          <t>J. HERRERO ALONSO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5821</v>
+        <v>0.6412</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2839</v>
+        <v>-0.4262</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2982</v>
+        <v>1.0675</v>
       </c>
       <c r="G8" t="n">
-        <v>1.7834</v>
+        <v>-1.421</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6554</v>
+        <v>3.2833</v>
       </c>
       <c r="I8" t="n">
-        <v>1.128</v>
+        <v>-4.7043</v>
       </c>
       <c r="J8" t="n">
-        <v>2.7293</v>
+        <v>1.0979</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3458</v>
+        <v>5.1465</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3835</v>
+        <v>-4.0486</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9459</v>
+        <v>-2.5189</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6904</v>
+        <v>-1.8632</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2555</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9308</v>
+        <v>-3.8616</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9308</v>
+        <v>2.51</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2592</v>
+        <v>1.5723</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8002</v>
+        <v>0.4959</v>
       </c>
       <c r="U8" t="n">
-        <v>0.541</v>
+        <v>1.0763</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9421</v>
+        <v>1.8415</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2856</v>
+        <v>1.8415</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6123</v>
+        <v>-2.0179</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4926</v>
+        <v>-0.07190000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.1198</v>
+        <v>-1.946</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2176</v>
@@ -1234,13 +1234,13 @@
         <v>1.7377</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0606</v>
+        <v>0.655</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1652</v>
+        <v>0.5858</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1046</v>
+        <v>0.0692</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2277</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7119</v>
+        <v>-3.2001</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.993</v>
+        <v>-1.4067</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7189</v>
+        <v>-1.7934</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9034</v>
@@ -1312,13 +1312,13 @@
         <v>0.5792</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8054</v>
+        <v>0.3172</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.1654</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2262</v>
+        <v>0.1518</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2277</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7326</v>
+        <v>-4.4358</v>
       </c>
       <c r="E12" t="n">
-        <v>1.1578</v>
+        <v>0.3304</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.8904</v>
+        <v>-4.7663</v>
       </c>
       <c r="G12" t="n">
         <v>-4.3802</v>
@@ -1390,13 +1390,13 @@
         <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8753</v>
+        <v>1.1721</v>
       </c>
       <c r="T12" t="n">
-        <v>1.7925</v>
+        <v>0.9651999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0828</v>
+        <v>0.2069</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2277</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.797199999999998</v>
+        <v>10.349</v>
       </c>
       <c r="E13" t="n">
-        <v>16.6979</v>
+        <v>17.2497</v>
       </c>
       <c r="F13" t="n">
-        <v>-6.900799999999999</v>
+        <v>-6.9008</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.411900000000001</v>
+        <v>-1.4119</v>
       </c>
       <c r="H13" t="n">
         <v>2.0693</v>
@@ -1447,7 +1447,7 @@
         <v>13.7997</v>
       </c>
       <c r="L13" t="n">
-        <v>3.8663</v>
+        <v>3.866300000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-19.078</v>
@@ -1468,16 +1468,16 @@
         <v>15.4463</v>
       </c>
       <c r="S13" t="n">
-        <v>5.7917</v>
+        <v>6.3436</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0655</v>
+        <v>2.6173</v>
       </c>
       <c r="U13" t="n">
-        <v>3.7262</v>
+        <v>3.7263</v>
       </c>
       <c r="V13" t="n">
-        <v>1.555800000000001</v>
+        <v>1.555799999999999</v>
       </c>
       <c r="W13" t="n">
         <v>8.5512</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.6434</v>
+        <v>4.3881</v>
       </c>
       <c r="E14" t="n">
-        <v>3.6095</v>
+        <v>3.713</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0339</v>
+        <v>0.6752</v>
       </c>
       <c r="G14" t="n">
         <v>4.774</v>
@@ -1546,13 +1546,13 @@
         <v>1.3515</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0279</v>
+        <v>-0.2274</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.607</v>
+        <v>-0.5036</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6349</v>
+        <v>0.2761</v>
       </c>
       <c r="V14" t="n">
         <v>0.6138</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.106</v>
+        <v>0.625</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2335</v>
+        <v>1.4404</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3395</v>
+        <v>-0.8154</v>
       </c>
       <c r="G15" t="n">
         <v>1.9762</v>
@@ -1624,13 +1624,13 @@
         <v>1.9308</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.9583</v>
+        <v>-1.2274</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1313</v>
+        <v>-0.9244</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.827</v>
+        <v>-0.3029</v>
       </c>
       <c r="V15" t="n">
         <v>1.2277</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4226</v>
+        <v>-0.1702</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4193</v>
+        <v>0.5228</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.842</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>0.5982</v>
@@ -1702,13 +1702,13 @@
         <v>0.5792</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5076000000000001</v>
+        <v>-0.2551</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1932</v>
+        <v>-0.0898</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3144</v>
+        <v>-0.1654</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8995</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DELICADO DOMINGUEZ</t>
+          <t>E. BUENO KNUTSEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4971</v>
+        <v>-0.3274</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4184</v>
+        <v>0.1078</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9155</v>
+        <v>-0.4353</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0243</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3521</v>
+        <v>-0.5726</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3278</v>
+        <v>0.6465</v>
       </c>
       <c r="J17" t="n">
-        <v>2.7427</v>
+        <v>1.4197</v>
       </c>
       <c r="K17" t="n">
-        <v>2.0079</v>
+        <v>0.1175</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7347</v>
+        <v>1.3022</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.7184</v>
+        <v>-1.3458</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6558</v>
+        <v>-0.6901</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0626</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3515</v>
+        <v>-0.3862</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9308</v>
+        <v>0.7723</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1271</v>
+        <v>-0.131</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0273</v>
+        <v>-0.2692</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0998</v>
+        <v>0.1382</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2277</v>
+        <v>-0.6565</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. BUENO KNUTSEN</t>
+          <t>A. DELICADO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6873</v>
+        <v>-0.9137</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.2024</v>
+        <v>1.2116</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4849</v>
+        <v>-2.1253</v>
       </c>
       <c r="G18" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.0243</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5726</v>
+        <v>0.3521</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6465</v>
+        <v>-0.3278</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4197</v>
+        <v>2.7427</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1175</v>
+        <v>2.0079</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3022</v>
+        <v>0.7347</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3458</v>
+        <v>-2.7184</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6901</v>
+        <v>-1.6558</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-1.0626</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.3862</v>
+        <v>-1.3515</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7723</v>
+        <v>1.9308</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4909</v>
+        <v>-0.2895</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5795</v>
+        <v>-0.1795</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0885</v>
+        <v>-0.1099</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6565</v>
+        <v>-1.2277</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. DIAZ CARBALLO</t>
+          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0627</v>
+        <v>-1.3184</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9528</v>
+        <v>3.0239</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1098</v>
+        <v>-4.3422</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6503</v>
+        <v>-0.3224</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.2071</v>
+        <v>-1.4211</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4431</v>
+        <v>1.0987</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.4699</v>
+        <v>2.8032</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5513</v>
+        <v>0.235</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0814</v>
+        <v>2.5682</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.1804</v>
+        <v>-3.1257</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6558</v>
+        <v>-1.6562</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5245</v>
+        <v>-1.4695</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.3169</v>
+        <v>1.1585</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0892</v>
+        <v>-0.3862</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7723</v>
+        <v>1.5446</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6768</v>
+        <v>-1.2549</v>
       </c>
       <c r="T19" t="n">
-        <v>1.3786</v>
+        <v>-0.6209</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2982</v>
+        <v>-0.6341</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2277</v>
+        <v>-0.8995</v>
       </c>
       <c r="W19" t="n">
         <v>1.2277</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-2.1271</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
+          <t>P. GRANJA I BERNAD</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.099</v>
+        <v>-1.9979</v>
       </c>
       <c r="E20" t="n">
-        <v>2.817</v>
+        <v>-0.7905</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.916</v>
+        <v>-1.2075</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3224</v>
+        <v>0.8915999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4211</v>
+        <v>0.4688</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0987</v>
+        <v>0.4227</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8032</v>
+        <v>1.368</v>
       </c>
       <c r="K20" t="n">
-        <v>0.235</v>
+        <v>1.3657</v>
       </c>
       <c r="L20" t="n">
-        <v>2.5682</v>
+        <v>0.0023</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.1257</v>
+        <v>-0.4764</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6562</v>
+        <v>-0.8969</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4695</v>
+        <v>0.4205</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1585</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.3862</v>
+        <v>-1.9308</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5446</v>
+        <v>0.7723</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.0356</v>
+        <v>-0.5033</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8277</v>
+        <v>-0.2277</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2078</v>
+        <v>-0.2757</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8995</v>
+        <v>-1.2277</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1271</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. GRANJA I BERNAD</t>
+          <t>D. DEL CERRO RUIZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2393</v>
+        <v>-2.5966</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8939</v>
+        <v>1.9153</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3454</v>
+        <v>-4.5119</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8915999999999999</v>
+        <v>-1.8934</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4688</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4227</v>
+        <v>-1.8176</v>
       </c>
       <c r="J21" t="n">
-        <v>1.368</v>
+        <v>1.2322</v>
       </c>
       <c r="K21" t="n">
-        <v>1.3657</v>
+        <v>1.7182</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0023</v>
+        <v>-0.486</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4764</v>
+        <v>-3.1257</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8969</v>
+        <v>-1.7941</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4205</v>
+        <v>-1.3316</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1585</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9308</v>
+        <v>-2.3169</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7723</v>
+        <v>1.7377</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7447</v>
+        <v>-0.7378</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3311</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4136</v>
+        <v>-0.0548</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2277</v>
+        <v>0.6138</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.6831</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2277</v>
+        <v>-3.0692</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1329</v>
+        <v>-2.8916</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.153</v>
+        <v>-2.0495</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.98</v>
+        <v>-0.8421</v>
       </c>
       <c r="G22" t="n">
         <v>-2.06</v>
@@ -2170,13 +2170,13 @@
         <v>0.1931</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5516</v>
+        <v>-0.3103</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4691</v>
+        <v>-0.3657</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0825</v>
+        <v>0.0554</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3282</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. DEL CERRO RUIZ</t>
+          <t>A. DIAZ CARBALLO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.1938</v>
+        <v>-3.2155</v>
       </c>
       <c r="E23" t="n">
-        <v>1.6051</v>
+        <v>-2.1939</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.7988</v>
+        <v>-1.0216</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.8934</v>
+        <v>-2.6503</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-2.2071</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.8176</v>
+        <v>-0.4431</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2322</v>
+        <v>-0.4699</v>
       </c>
       <c r="K23" t="n">
-        <v>1.7182</v>
+        <v>-0.5513</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.486</v>
+        <v>0.0814</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.1257</v>
+        <v>-2.1804</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.7941</v>
+        <v>-1.6558</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.3316</v>
+        <v>-0.5245</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5792</v>
+        <v>-2.3169</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.3169</v>
+        <v>-3.0892</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7377</v>
+        <v>0.7723</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3349</v>
+        <v>0.524</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9933</v>
+        <v>0.1375</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3417</v>
+        <v>0.3865</v>
       </c>
       <c r="V23" t="n">
-        <v>0.6138</v>
+        <v>1.2277</v>
       </c>
       <c r="W23" t="n">
-        <v>3.6831</v>
+        <v>1.2277</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.0692</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,22 +2281,22 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.7973</v>
+        <v>-8.418200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>6.900700000000001</v>
+        <v>6.900900000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.698</v>
+        <v>-15.3191</v>
       </c>
       <c r="G24" t="n">
-        <v>1.412099999999999</v>
+        <v>1.4121</v>
       </c>
       <c r="H24" t="n">
         <v>-2.0691</v>
       </c>
       <c r="I24" t="n">
-        <v>3.4812</v>
+        <v>3.481200000000001</v>
       </c>
       <c r="J24" t="n">
         <v>19.0779</v>
@@ -2305,7 +2305,7 @@
         <v>11.7303</v>
       </c>
       <c r="L24" t="n">
-        <v>7.3475</v>
+        <v>7.347500000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-17.6662</v>
@@ -2326,13 +2326,13 @@
         <v>11.5846</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.7918</v>
+        <v>-4.4127</v>
       </c>
       <c r="T24" t="n">
         <v>-3.7263</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.0656</v>
+        <v>-0.6866000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5561</v>
